--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T10:55:45+00:00</t>
+    <t>2023-04-05T15:18:36+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:18:36+00:00</t>
+    <t>2023-04-05T15:41:27+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:41:27+00:00</t>
+    <t>2023-04-05T15:52:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1779,7 +1779,7 @@
     <t>Practitioner.address</t>
   </si>
   <si>
-    <t xml:space="preserve">Address {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/fr-address-extended}
+    <t xml:space="preserve">Address {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-address-extended}
 </t>
   </si>
   <si>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:52:08+00:00</t>
+    <t>2023-04-05T15:53:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:53:16+00:00</t>
+    <t>2023-04-05T15:55:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T15:55:13+00:00</t>
+    <t>2023-04-05T16:00:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:00:25+00:00</t>
+    <t>2023-04-05T16:20:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:20:25+00:00</t>
+    <t>2023-04-05T16:21:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T16:21:30+00:00</t>
+    <t>2023-04-05T16:24:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-05T17:39:15+00:00</t>
+    <t>2023-04-07T12:42:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:00:48+00:00</t>
+    <t>2023-04-12T10:05:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -57,7 +57,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T10:05:52+00:00</t>
+    <t>2023-04-12T10:08:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-12T14:03:54+00:00</t>
+    <t>2023-04-13T07:49:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T07:49:09+00:00</t>
+    <t>2023-04-13T08:12:13+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:12:13+00:00</t>
+    <t>2023-04-13T08:22:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:22:34+00:00</t>
+    <t>2023-04-13T08:33:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:33:21+00:00</t>
+    <t>2023-04-13T08:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T08:54:00+00:00</t>
+    <t>2023-04-13T09:51:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T09:51:53+00:00</t>
+    <t>2023-04-13T10:21:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T10:21:56+00:00</t>
+    <t>2023-04-13T12:58:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T12:58:26+00:00</t>
+    <t>2023-04-13T15:00:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:00:08+00:00</t>
+    <t>2023-04-13T15:16:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-13T15:16:05+00:00</t>
+    <t>2023-04-14T12:31:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:31:23+00:00</t>
+    <t>2023-04-14T12:45:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T12:45:28+00:00</t>
+    <t>2023-04-14T13:02:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:02:26+00:00</t>
+    <t>2023-04-14T13:12:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-14T13:12:31+00:00</t>
+    <t>2023-04-17T08:15:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:15:24+00:00</t>
+    <t>2023-04-17T08:17:23+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:17:23+00:00</t>
+    <t>2023-04-17T08:37:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T08:37:32+00:00</t>
+    <t>2023-04-17T09:07:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T09:07:20+00:00</t>
+    <t>2023-04-17T10:39:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:39:40+00:00</t>
+    <t>2023-04-17T10:56:20+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T10:56:20+00:00</t>
+    <t>2023-04-17T11:14:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:14:19+00:00</t>
+    <t>2023-04-17T11:17:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:17:21+00:00</t>
+    <t>2023-04-17T11:39:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:39:02+00:00</t>
+    <t>2023-04-17T11:54:58+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T11:54:58+00:00</t>
+    <t>2023-04-17T12:02:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T12:02:32+00:00</t>
+    <t>2023-04-17T13:37:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-17T14:05:09+00:00</t>
+    <t>2023-04-20T17:39:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:42:03+00:00</t>
+    <t>2023-04-20T17:43:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:10+00:00</t>
+    <t>2023-04-20T17:43:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-20T17:43:52+00:00</t>
+    <t>2023-04-28T11:09:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -650,7 +650,7 @@
 </t>
   </si>
   <si>
-    <t>lieuNaissance</t>
+    <t>[DR] : lieuNaissance</t>
   </si>
   <si>
     <t>Code officiel géographique (COG) de la commune (France) ou du pays</t>
@@ -666,7 +666,7 @@
 </t>
   </si>
   <si>
-    <t>dateDeces</t>
+    <t>[DR] : dateDeces</t>
   </si>
   <si>
     <t>Date de décès de la personne</t>
@@ -1124,7 +1124,7 @@
 </t>
   </si>
   <si>
-    <t>Family name (often called 'Surname')</t>
+    <t>[DR] : nomFamille/nomUsage</t>
   </si>
   <si>
     <t>The part of a name that links to the genealogy. In some cultures (e.g. Eritrea) the family name of a son is the first name of his father.</t>
@@ -1152,7 +1152,7 @@
 middle name</t>
   </si>
   <si>
-    <t>Given names (not always 'first'). Includes middle names</t>
+    <t>[DR] : prenom/prenomUsuel</t>
   </si>
   <si>
     <t>Given name.</t>
@@ -1255,7 +1255,7 @@
 </t>
   </si>
   <si>
-    <t>Details of a Technology mediated contact point (phone, fax, email, etc.)</t>
+    <t>[DR] : telecommunication</t>
   </si>
   <si>
     <t>Details for all kinds of technology mediated contact points for a person or organization, including telephone, email, etc.</t>
@@ -1428,7 +1428,7 @@
 </t>
   </si>
   <si>
-    <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats)</t>
+    <t>[DR] : adresseCorrespondance</t>
   </si>
   <si>
     <t>An address expressed using postal conventions (as opposed to GPS or other location definition formats).  This data type may be used to convey addresses for use in delivering mail as well as for visiting locations which might not be valid for mail delivery.  There are a variety of postal address formats defined around the world.</t>
@@ -1452,7 +1452,7 @@
     <t>Practitioner.gender</t>
   </si>
   <si>
-    <t>male | female | other | unknown</t>
+    <t>[DR] : sexeAdministratif</t>
   </si>
   <si>
     <t>Administrative Gender - the gender that the person is considered to have for administration and record keeping purposes.</t>
@@ -1483,7 +1483,7 @@
 </t>
   </si>
   <si>
-    <t>The date  on which the practitioner was born</t>
+    <t>[DR] - dateNaissance</t>
   </si>
   <si>
     <t>The date of birth for the practitioner.</t>
@@ -1584,7 +1584,7 @@
     <t>Practitioner.qualification.identifier</t>
   </si>
   <si>
-    <t>Numéro de diplôme</t>
+    <t>numeroDiplome</t>
   </si>
   <si>
     <t>An identifier that applies to this person's qualification in this role.</t>
@@ -2476,7 +2476,7 @@
 </t>
   </si>
   <si>
-    <t>Concept - reference to a terminology or just  text</t>
+    <t>langueParlee</t>
   </si>
   <si>
     <t>A concept that may be defined by a formal reference to a terminology or ontology or may be provided by text.</t>
@@ -9719,7 +9719,7 @@
         <v>77</v>
       </c>
       <c r="H61" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I61" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T15:03:41+00:00</t>
+    <t>2023-04-28T18:35:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:35:22+00:00</t>
+    <t>2023-04-28T18:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -4408,7 +4408,7 @@
         <v>77</v>
       </c>
       <c r="H19" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I19" t="s" s="2">
         <v>75</v>
@@ -4636,7 +4636,7 @@
         <v>77</v>
       </c>
       <c r="H21" t="s" s="2">
-        <v>75</v>
+        <v>86</v>
       </c>
       <c r="I21" t="s" s="2">
         <v>75</v>
@@ -9532,7 +9532,7 @@
         <v>97</v>
       </c>
       <c r="AJ63" t="s" s="2">
-        <v>75</v>
+        <v>98</v>
       </c>
       <c r="AK63" t="s" s="2">
         <v>498</v>
@@ -9910,7 +9910,7 @@
         <v>85</v>
       </c>
       <c r="H67" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I67" t="s" s="2">
         <v>75</v>
@@ -10028,7 +10028,7 @@
         <v>85</v>
       </c>
       <c r="H68" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I68" t="s" s="2">
         <v>75</v>
@@ -10146,7 +10146,7 @@
         <v>85</v>
       </c>
       <c r="H69" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I69" t="s" s="2">
         <v>75</v>
@@ -10264,7 +10264,7 @@
         <v>85</v>
       </c>
       <c r="H70" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I70" t="s" s="2">
         <v>75</v>
@@ -10382,7 +10382,7 @@
         <v>85</v>
       </c>
       <c r="H71" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I71" t="s" s="2">
         <v>75</v>
@@ -10500,7 +10500,7 @@
         <v>85</v>
       </c>
       <c r="H72" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I72" t="s" s="2">
         <v>75</v>
@@ -10618,7 +10618,7 @@
         <v>85</v>
       </c>
       <c r="H73" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I73" t="s" s="2">
         <v>75</v>
@@ -10736,7 +10736,7 @@
         <v>85</v>
       </c>
       <c r="H74" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I74" t="s" s="2">
         <v>75</v>
@@ -10854,7 +10854,7 @@
         <v>85</v>
       </c>
       <c r="H75" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I75" t="s" s="2">
         <v>75</v>
@@ -10972,7 +10972,7 @@
         <v>85</v>
       </c>
       <c r="H76" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I76" t="s" s="2">
         <v>75</v>
@@ -11090,7 +11090,7 @@
         <v>85</v>
       </c>
       <c r="H77" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I77" t="s" s="2">
         <v>75</v>
@@ -11208,7 +11208,7 @@
         <v>85</v>
       </c>
       <c r="H78" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I78" t="s" s="2">
         <v>75</v>
@@ -11326,7 +11326,7 @@
         <v>85</v>
       </c>
       <c r="H79" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I79" t="s" s="2">
         <v>75</v>
@@ -11444,7 +11444,7 @@
         <v>85</v>
       </c>
       <c r="H80" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I80" t="s" s="2">
         <v>75</v>
@@ -11562,7 +11562,7 @@
         <v>85</v>
       </c>
       <c r="H81" t="s" s="2">
-        <v>86</v>
+        <v>75</v>
       </c>
       <c r="I81" t="s" s="2">
         <v>75</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:37:07+00:00</t>
+    <t>2023-04-28T18:58:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-04-28T18:58:16+00:00</t>
+    <t>2023-05-02T06:31:09+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:31:09+00:00</t>
+    <t>2023-05-02T06:34:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T06:34:44+00:00</t>
+    <t>2023-05-02T07:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:04:27+00:00</t>
+    <t>2023-05-02T14:10:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -859,13 +859,13 @@
     <t>Practitioner.active</t>
   </si>
   <si>
-    <t>Whether this practitioner's record is in active use</t>
+    <t>isActive</t>
   </si>
   <si>
     <t>Whether this practitioner's record is in active use.</t>
   </si>
   <si>
-    <t>If the practitioner is not in use by one organization, then it should mark the period on the PractitonerRole with an end date (even if they are active) as they may be active in another role.</t>
+    <t>true  par défaut; false pour les professionnels supprimés</t>
   </si>
   <si>
     <t>Need to be able to mark a practitioner record as not to be used because it was created in error.</t>
@@ -6060,7 +6060,7 @@
         <v>78</v>
       </c>
       <c r="H36" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I36" t="s" s="2">
         <v>71</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:10:11+00:00</t>
+    <t>2023-05-02T14:20:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:20:51+00:00</t>
+    <t>2023-05-02T14:32:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T14:32:14+00:00</t>
+    <t>2023-05-02T15:50:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T15:50:41+00:00</t>
+    <t>2023-05-02T16:15:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T16:15:55+00:00</t>
+    <t>2023-05-02T17:25:18+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:25:18+00:00</t>
+    <t>2023-05-02T17:45:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-02T17:45:11+00:00</t>
+    <t>2023-05-02T17:46:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3804,7 +3804,7 @@
         <v>73</v>
       </c>
       <c r="H14" t="s" s="2">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="I14" t="s" s="2">
         <v>71</v>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:01:59+00:00</t>
+    <t>2023-05-04T14:04:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:04:48+00:00</t>
+    <t>2023-05-04T14:08:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
+++ b/ig/feature-good-practices-interop/StructureDefinition-as-practitioner.xlsx
@@ -60,7 +60,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2023-05-04T14:08:50+00:00</t>
+    <t>2023-05-05T17:21:25+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -429,13 +429,13 @@
 ext-1:Must have either extensions or value[x], not both {extension.exists() != value.exists()}</t>
   </si>
   <si>
-    <t>Practitioner.extension:practitioner-nationality</t>
-  </si>
-  <si>
-    <t>practitioner-nationality</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/practitioner-nationality}
+    <t>Practitioner.extension:as-ext-practitioner-nationality</t>
+  </si>
+  <si>
+    <t>as-ext-practitioner-nationality</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-practitioner-nationality}
 </t>
   </si>
   <si>
@@ -445,13 +445,13 @@
     <t>Nationalité de la personne</t>
   </si>
   <si>
-    <t>Practitioner.extension:practitioner-authorization</t>
-  </si>
-  <si>
-    <t>practitioner-authorization</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/practitioner-authorization}
+    <t>Practitioner.extension:as-ext-practitioner-authorization</t>
+  </si>
+  <si>
+    <t>as-ext-practitioner-authorization</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-practitioner-authorization}
 </t>
   </si>
   <si>
@@ -461,13 +461,13 @@
     <t>L'autorisation d'exercice pour les personnes diposant de diplômes étrangers non reconnus en France</t>
   </si>
   <si>
-    <t>Practitioner.extension:practitioner-birthPlace</t>
-  </si>
-  <si>
-    <t>practitioner-birthPlace</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/practitioner-birthPlace}
+    <t>Practitioner.extension:as-ext-practitioner-birth-place</t>
+  </si>
+  <si>
+    <t>as-ext-practitioner-birth-place</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-practitioner-birth-place}
 </t>
   </si>
   <si>
@@ -477,13 +477,13 @@
     <t>Code officiel géographique (COG) de la commune (France) ou du pays</t>
   </si>
   <si>
-    <t>Practitioner.extension:practitioner-deceasedDateTime</t>
-  </si>
-  <si>
-    <t>practitioner-deceasedDateTime</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/practitioner-deceasedDateTime}
+    <t>Practitioner.extension:as-ext-practitioner-deceased-date-time</t>
+  </si>
+  <si>
+    <t>as-ext-practitioner-deceased-date-time</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-ext-practitioner-deceased-date-time}
 </t>
   </si>
   <si>
@@ -2125,7 +2125,7 @@
     <t>Practitioner.communication</t>
   </si>
   <si>
-    <t xml:space="preserve">CodeableConcept {https://apifhir.annuaire.sante.fr/ws-sync/exposed/structuredefinition/codeableConcept-timed}
+    <t xml:space="preserve">CodeableConcept {http://interop.esante.gouv.fr/ig/fhir/annuaire-donnee-publique/StructureDefinition/as-codeableconcept-timed}
 </t>
   </si>
   <si>
@@ -2452,7 +2452,7 @@
   <cols>
     <col min="1" max="1" width="59.60546875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="47.9140625" customWidth="true" bestFit="true"/>
-    <col min="3" max="3" width="30.09765625" customWidth="true" bestFit="true" hidden="true"/>
+    <col min="3" max="3" width="37.10546875" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="39.9140625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="5" max="5" width="6.77734375" customWidth="true" bestFit="true"/>
     <col min="6" max="6" width="4.9453125" customWidth="true" bestFit="true"/>
@@ -2460,7 +2460,7 @@
     <col min="8" max="8" width="16.27734375" customWidth="true" bestFit="true"/>
     <col min="9" max="9" width="13.26171875" customWidth="true" bestFit="true"/>
     <col min="10" max="10" width="20.703125" customWidth="true" bestFit="true"/>
-    <col min="11" max="11" width="106.27734375" customWidth="true" bestFit="true"/>
+    <col min="11" max="11" width="124.64453125" customWidth="true" bestFit="true"/>
     <col min="12" max="12" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="13" max="13" width="100.703125" customWidth="true" bestFit="true"/>
     <col min="14" max="14" width="100.703125" customWidth="true" bestFit="true"/>
